--- a/output/pdf_financials_xlsx/GOR.xlsx
+++ b/output/pdf_financials_xlsx/GOR.xlsx
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.803586</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.803586</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.803586</v>
       </c>
     </row>
     <row r="93">
@@ -3120,7 +3120,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3389,7 +3393,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>2.803586</v>
       </c>

--- a/output/pdf_financials_xlsx/GOR.xlsx
+++ b/output/pdf_financials_xlsx/GOR.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000875</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001886</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002249</v>
       </c>
     </row>
     <row r="13">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.266837</v>
+        <v>-0.267712</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.213301</v>
+        <v>-0.215187</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.268404</v>
+        <v>-0.270653</v>
       </c>
     </row>
     <row r="28">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.266369</v>
+        <v>-0.267244</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.212953</v>
+        <v>-0.214839</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.267335</v>
+        <v>-0.269584</v>
       </c>
     </row>
     <row r="30">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">

--- a/output/pdf_financials_xlsx/GOR.xlsx
+++ b/output/pdf_financials_xlsx/GOR.xlsx
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.015851</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.015429</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -3488,7 +3488,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.015851</v>
       </c>
